--- a/samples/home_services-full.xlsx
+++ b/samples/home_services-full.xlsx
@@ -4140,147 +4140,147 @@
         <v>156</v>
       </c>
       <c r="C11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-C34/Inputs!$E$13)</f>
+        <f aca="false">-C34/MAX(1,Inputs!$E$13)</f>
         <v>180</v>
       </c>
       <c r="D11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-D34/Inputs!$E$13)</f>
+        <f aca="false">-D34/MAX(1,Inputs!$E$13)</f>
         <v>180</v>
       </c>
       <c r="E11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-E34/Inputs!$E$13)</f>
+        <f aca="false">-E34/MAX(1,Inputs!$E$13)</f>
         <v>180</v>
       </c>
       <c r="F11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-F34/Inputs!$E$13)</f>
+        <f aca="false">-F34/MAX(1,Inputs!$E$13)</f>
         <v>180</v>
       </c>
       <c r="G11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-G34/Inputs!$E$13)</f>
+        <f aca="false">-G34/MAX(1,Inputs!$E$13)</f>
         <v>180</v>
       </c>
       <c r="H11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-H34/Inputs!$E$13)</f>
+        <f aca="false">-H34/MAX(1,Inputs!$E$13)</f>
         <v>180</v>
       </c>
       <c r="I11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-I34/Inputs!$E$13)</f>
+        <f aca="false">-I34/MAX(1,Inputs!$E$13)</f>
         <v>180</v>
       </c>
       <c r="J11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-J34/Inputs!$E$13)</f>
+        <f aca="false">-J34/MAX(1,Inputs!$E$13)</f>
         <v>180</v>
       </c>
       <c r="K11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-K34/Inputs!$E$13)</f>
+        <f aca="false">-K34/MAX(1,Inputs!$E$13)</f>
         <v>180</v>
       </c>
       <c r="L11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-L34/Inputs!$E$13)</f>
+        <f aca="false">-L34/MAX(1,Inputs!$E$13)</f>
         <v>180</v>
       </c>
       <c r="M11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-M34/Inputs!$E$13)</f>
+        <f aca="false">-M34/MAX(1,Inputs!$E$13)</f>
         <v>180</v>
       </c>
       <c r="N11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-N34/Inputs!$E$13)</f>
+        <f aca="false">-N34/MAX(1,Inputs!$E$13)</f>
         <v>180</v>
       </c>
       <c r="O11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-O34/Inputs!$E$13)</f>
+        <f aca="false">-O34/MAX(1,Inputs!$E$13)</f>
         <v>207</v>
       </c>
       <c r="P11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-P34/Inputs!$E$13)</f>
+        <f aca="false">-P34/MAX(1,Inputs!$E$13)</f>
         <v>207</v>
       </c>
       <c r="Q11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-Q34/Inputs!$E$13)</f>
+        <f aca="false">-Q34/MAX(1,Inputs!$E$13)</f>
         <v>207</v>
       </c>
       <c r="R11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-R34/Inputs!$E$13)</f>
+        <f aca="false">-R34/MAX(1,Inputs!$E$13)</f>
         <v>207</v>
       </c>
       <c r="S11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-S34/Inputs!$E$13)</f>
+        <f aca="false">-S34/MAX(1,Inputs!$E$13)</f>
         <v>207</v>
       </c>
       <c r="T11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-T34/Inputs!$E$13)</f>
+        <f aca="false">-T34/MAX(1,Inputs!$E$13)</f>
         <v>207</v>
       </c>
       <c r="U11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-U34/Inputs!$E$13)</f>
+        <f aca="false">-U34/MAX(1,Inputs!$E$13)</f>
         <v>207</v>
       </c>
       <c r="V11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-V34/Inputs!$E$13)</f>
+        <f aca="false">-V34/MAX(1,Inputs!$E$13)</f>
         <v>207</v>
       </c>
       <c r="W11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-W34/Inputs!$E$13)</f>
+        <f aca="false">-W34/MAX(1,Inputs!$E$13)</f>
         <v>207</v>
       </c>
       <c r="X11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-X34/Inputs!$E$13)</f>
+        <f aca="false">-X34/MAX(1,Inputs!$E$13)</f>
         <v>207</v>
       </c>
       <c r="Y11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-Y34/Inputs!$E$13)</f>
+        <f aca="false">-Y34/MAX(1,Inputs!$E$13)</f>
         <v>207</v>
       </c>
       <c r="Z11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-Z34/Inputs!$E$13)</f>
+        <f aca="false">-Z34/MAX(1,Inputs!$E$13)</f>
         <v>207</v>
       </c>
       <c r="AA11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-AA34/Inputs!$E$13)</f>
+        <f aca="false">-AA34/MAX(1,Inputs!$E$13)</f>
         <v>238.05</v>
       </c>
       <c r="AB11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-AB34/Inputs!$E$13)</f>
+        <f aca="false">-AB34/MAX(1,Inputs!$E$13)</f>
         <v>238.05</v>
       </c>
       <c r="AC11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-AC34/Inputs!$E$13)</f>
+        <f aca="false">-AC34/MAX(1,Inputs!$E$13)</f>
         <v>238.05</v>
       </c>
       <c r="AD11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-AD34/Inputs!$E$13)</f>
+        <f aca="false">-AD34/MAX(1,Inputs!$E$13)</f>
         <v>238.05</v>
       </c>
       <c r="AE11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-AE34/Inputs!$E$13)</f>
+        <f aca="false">-AE34/MAX(1,Inputs!$E$13)</f>
         <v>238.05</v>
       </c>
       <c r="AF11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-AF34/Inputs!$E$13)</f>
+        <f aca="false">-AF34/MAX(1,Inputs!$E$13)</f>
         <v>238.05</v>
       </c>
       <c r="AG11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-AG34/Inputs!$E$13)</f>
+        <f aca="false">-AG34/MAX(1,Inputs!$E$13)</f>
         <v>238.05</v>
       </c>
       <c r="AH11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-AH34/Inputs!$E$13)</f>
+        <f aca="false">-AH34/MAX(1,Inputs!$E$13)</f>
         <v>238.05</v>
       </c>
       <c r="AI11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-AI34/Inputs!$E$13)</f>
+        <f aca="false">-AI34/MAX(1,Inputs!$E$13)</f>
         <v>238.05</v>
       </c>
       <c r="AJ11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-AJ34/Inputs!$E$13)</f>
+        <f aca="false">-AJ34/MAX(1,Inputs!$E$13)</f>
         <v>238.05</v>
       </c>
       <c r="AK11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-AK34/Inputs!$E$13)</f>
+        <f aca="false">-AK34/MAX(1,Inputs!$E$13)</f>
         <v>238.05</v>
       </c>
       <c r="AL11" s="19" t="n">
-        <f aca="false">IF(Inputs!$E$13=0,0,-AL34/Inputs!$E$13)</f>
+        <f aca="false">-AL34/MAX(1,Inputs!$E$13)</f>
         <v>238.05</v>
       </c>
     </row>
